--- a/data/n5/n5_comparison.xlsx
+++ b/data/n5/n5_comparison.xlsx
@@ -739,7 +739,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>ほしい(명사+がほしい: 사물 소망) vs たい(動詞stem+たい: 동작 소망).</t>
+          <t>ほしい(명사+がほしい: 사물 소망) vs たい(동사 ます형+たい: 동작 소망).</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>ほしい(명사+がほしい: 사물 소망)와 たい(動詞stem+たい: 동작 소망). 접속 구조 차이.</t>
+          <t>ほしい(명사+がほしい: 사물 소망)와 たい(동사 ます형+たい: 동작 소망). 접속 구조 차이.</t>
         </is>
       </c>
     </row>
